--- a/Scenario Files/ShowerRAGScenarios.xlsx
+++ b/Scenario Files/ShowerRAGScenarios.xlsx
@@ -669,7 +669,7 @@
         <v>0.76</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.819</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -747,7 +747,7 @@
         <v>0.67</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.6715</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -903,7 +903,7 @@
         <v>0.46</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1137,7 +1137,7 @@
         <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7324999999999999</v>
+        <v>0.7325</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1215,7 +1215,7 @@
         <v>0.85</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7064999999999999</v>
+        <v>0.7065</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>0.15</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -1761,7 +1761,7 @@
         <v>0.22</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2619,7 +2619,7 @@
         <v>0.31</v>
       </c>
       <c r="R28" t="n">
-        <v>0.6729999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -2931,7 +2931,7 @@
         <v>0.22</v>
       </c>
       <c r="R32" t="n">
-        <v>0.7529999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3087,7 +3087,7 @@
         <v>0.46</v>
       </c>
       <c r="R34" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3165,7 +3165,7 @@
         <v>0.22</v>
       </c>
       <c r="R35" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -3243,7 +3243,7 @@
         <v>0.35</v>
       </c>
       <c r="R36" t="n">
-        <v>0.7905000000000001</v>
+        <v>0.7905</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -3399,7 +3399,7 @@
         <v>0.29</v>
       </c>
       <c r="R38" t="n">
-        <v>0.7625000000000001</v>
+        <v>0.7625</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -3633,7 +3633,7 @@
         <v>0.22</v>
       </c>
       <c r="R41" t="n">
-        <v>0.7380000000000001</v>
+        <v>0.738</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -3711,7 +3711,7 @@
         <v>0.35</v>
       </c>
       <c r="R42" t="n">
-        <v>0.7294999999999999</v>
+        <v>0.7295</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -3867,7 +3867,7 @@
         <v>0.22</v>
       </c>
       <c r="R44" t="n">
-        <v>0.7529999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -4023,7 +4023,7 @@
         <v>0.46</v>
       </c>
       <c r="R46" t="n">
-        <v>0.6539999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -4101,7 +4101,7 @@
         <v>0.22</v>
       </c>
       <c r="R47" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -4335,7 +4335,7 @@
         <v>0.22</v>
       </c>
       <c r="R50" t="n">
-        <v>0.7589999999999999</v>
+        <v>0.759</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -4491,7 +4491,7 @@
         <v>0.46</v>
       </c>
       <c r="R52" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -4569,7 +4569,7 @@
         <v>0.15</v>
       </c>
       <c r="R53" t="n">
-        <v>0.6329999999999999</v>
+        <v>0.633</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -4803,7 +4803,7 @@
         <v>0.29</v>
       </c>
       <c r="R56" t="n">
-        <v>0.7794999999999999</v>
+        <v>0.7795</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -4959,7 +4959,7 @@
         <v>0.85</v>
       </c>
       <c r="R58" t="n">
-        <v>0.8109999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="S58" t="n">
         <v>2</v>
@@ -5037,7 +5037,7 @@
         <v>0.15</v>
       </c>
       <c r="R59" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -5115,7 +5115,7 @@
         <v>0.46</v>
       </c>
       <c r="R60" t="n">
-        <v>0.6379999999999999</v>
+        <v>0.638</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -5193,7 +5193,7 @@
         <v>0.67</v>
       </c>
       <c r="R61" t="n">
-        <v>0.4985000000000001</v>
+        <v>0.4985</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>

--- a/Scenario Files/ShowerRAGScenarios.xlsx
+++ b/Scenario Files/ShowerRAGScenarios.xlsx
@@ -597,10 +597,10 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="V2" t="n">
         <v>10</v>
@@ -675,10 +675,10 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="V3" t="n">
         <v>16</v>
@@ -753,10 +753,10 @@
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.547530455171008</v>
+        <v>2.343728018757327</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4453083235638921</v>
       </c>
       <c r="V4" t="n">
         <v>24</v>
@@ -831,10 +831,10 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3268387787349</v>
+        <v>1.220691676436108</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2520993679596309</v>
+        <v>0.2319314185228604</v>
       </c>
       <c r="V5" t="n">
         <v>12.5</v>
@@ -909,10 +909,10 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12294204597584</v>
+        <v>1.953106682297772</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4033589887354095</v>
+        <v>0.3710902696365768</v>
       </c>
       <c r="V6" t="n">
         <v>20</v>
@@ -969,7 +969,7 @@
         <v>12</v>
       </c>
       <c r="N7" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="O7" t="n">
         <v>0.38</v>
@@ -981,16 +981,16 @@
         <v>0.67</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5765</v>
+        <v>0.5825</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.18441306896376</v>
+        <v>2.929660023446659</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6050384831031144</v>
+        <v>0.5566354044548653</v>
       </c>
       <c r="V7" t="n">
         <v>30</v>
@@ -1065,10 +1065,10 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.115778842768697</v>
+        <v>1.043845666931795</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2119979801260525</v>
+        <v>0.198330676717041</v>
       </c>
       <c r="V8" t="n">
         <v>8</v>
@@ -1143,10 +1143,10 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.673668264153046</v>
+        <v>1.565768500397692</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3179969701890787</v>
+        <v>0.2974960150755615</v>
       </c>
       <c r="V9" t="n">
         <v>12</v>
@@ -1221,10 +1221,10 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="V10" t="n">
         <v>20</v>
@@ -1299,10 +1299,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.916444458800617</v>
+        <v>0.8509510795479465</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1741244471721172</v>
+        <v>0.1616807051141098</v>
       </c>
       <c r="V11" t="n">
         <v>7.5</v>
@@ -1377,10 +1377,10 @@
         <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.527407431334362</v>
+        <v>1.418251799246577</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2902074119535287</v>
+        <v>0.2694678418568497</v>
       </c>
       <c r="V12" t="n">
         <v>12.5</v>
@@ -1455,10 +1455,10 @@
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.443851890134979</v>
+        <v>2.269202878794524</v>
       </c>
       <c r="U13" t="n">
-        <v>0.464331859125646</v>
+        <v>0.4311485469709595</v>
       </c>
       <c r="V13" t="n">
         <v>20</v>
@@ -1533,10 +1533,10 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.010866009101286</v>
+        <v>0.9336069641199739</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1920645417292444</v>
+        <v>0.177385323182795</v>
       </c>
       <c r="V14" t="n">
         <v>9</v>
@@ -1593,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O15" t="n">
         <v>0.85</v>
@@ -1605,16 +1605,16 @@
         <v>0.29</v>
       </c>
       <c r="R15" t="n">
-        <v>0.729</v>
+        <v>0.732</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.347821345468382</v>
+        <v>1.244809285493299</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2560860556389926</v>
+        <v>0.2365137642437267</v>
       </c>
       <c r="V15" t="n">
         <v>12</v>
@@ -1680,19 +1680,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0.654</v>
+        <v>0.7065</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.021732018202572</v>
+        <v>1.867213928239948</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3841290834584888</v>
+        <v>0.3547706463655901</v>
       </c>
       <c r="V16" t="n">
         <v>18</v>
@@ -1767,10 +1767,10 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.955323920689128</v>
+        <v>0.8995966919822622</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1815115449309343</v>
+        <v>0.1709233714766298</v>
       </c>
       <c r="V17" t="n">
         <v>6</v>
@@ -1845,10 +1845,10 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.59220653448188</v>
+        <v>1.499327819970437</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2848722857943831</v>
       </c>
       <c r="V18" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="O19" t="n">
         <v>0.74</v>
@@ -1917,16 +1917,16 @@
         <v>0.76</v>
       </c>
       <c r="R19" t="n">
-        <v>0.745</v>
+        <v>0.742</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.547530455171008</v>
+        <v>2.398924511952699</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4840307864824915</v>
+        <v>0.4557956572710128</v>
       </c>
       <c r="V19" t="n">
         <v>16</v>
@@ -2001,10 +2001,10 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.916444458800617</v>
+        <v>0.8509510795479465</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1741244471721172</v>
+        <v>0.1616807051141098</v>
       </c>
       <c r="V20" t="n">
         <v>7.5</v>
@@ -2079,10 +2079,10 @@
         <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.527407431334362</v>
+        <v>1.418251799246577</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2902074119535287</v>
+        <v>0.2694678418568497</v>
       </c>
       <c r="V21" t="n">
         <v>12.5</v>
@@ -2157,10 +2157,10 @@
         <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.443851890134979</v>
+        <v>2.269202878794524</v>
       </c>
       <c r="U22" t="n">
-        <v>0.464331859125646</v>
+        <v>0.4311485469709595</v>
       </c>
       <c r="V22" t="n">
         <v>20</v>
@@ -2235,10 +2235,10 @@
         <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>0.636882613792752</v>
+        <v>0.5859320046893317</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.111327080890973</v>
       </c>
       <c r="V23" t="n">
         <v>6</v>
@@ -2313,10 +2313,10 @@
         <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.06147102298792</v>
+        <v>0.9765533411488861</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2016794943677048</v>
+        <v>0.1855451348182884</v>
       </c>
       <c r="V24" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.698353636780672</v>
+        <v>1.562485345838218</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3226871909883277</v>
+        <v>0.2968722157092614</v>
       </c>
       <c r="V25" t="n">
         <v>16</v>
@@ -2469,10 +2469,10 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9812435619481353</v>
+        <v>0.9147781961482522</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1864362767701457</v>
+        <v>0.1738078572681679</v>
       </c>
       <c r="V26" t="n">
         <v>7.5</v>
@@ -2547,10 +2547,10 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.635405936580226</v>
+        <v>1.524630326913754</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3107271279502429</v>
+        <v>0.2896797621136132</v>
       </c>
       <c r="V27" t="n">
         <v>12.5</v>
@@ -2607,7 +2607,7 @@
         <v>7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="O28" t="n">
         <v>0.71</v>
@@ -2619,16 +2619,16 @@
         <v>0.31</v>
       </c>
       <c r="R28" t="n">
-        <v>0.673</v>
+        <v>0.676</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.289568311212316</v>
+        <v>2.134482457679255</v>
       </c>
       <c r="U28" t="n">
-        <v>0.43501797913034</v>
+        <v>0.4055516669590585</v>
       </c>
       <c r="V28" t="n">
         <v>17.5</v>
@@ -2703,10 +2703,10 @@
         <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>0.7331555670404936</v>
+        <v>0.6807608636383572</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1392995577376938</v>
+        <v>0.1293445640912879</v>
       </c>
       <c r="V29" t="n">
         <v>6</v>
@@ -2781,10 +2781,10 @@
         <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.221925945067489</v>
+        <v>1.134601439397262</v>
       </c>
       <c r="U30" t="n">
-        <v>0.232165929562823</v>
+        <v>0.2155742734854798</v>
       </c>
       <c r="V30" t="n">
         <v>10</v>
@@ -2859,10 +2859,10 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1.955081512107983</v>
+        <v>1.815362303035619</v>
       </c>
       <c r="U31" t="n">
-        <v>0.3714654873005167</v>
+        <v>0.3449188375767677</v>
       </c>
       <c r="V31" t="n">
         <v>16</v>
@@ -2937,10 +2937,10 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1.046042665095654</v>
+        <v>0.9786053127485578</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1987481063681742</v>
+        <v>0.185935009422226</v>
       </c>
       <c r="V32" t="n">
         <v>7.5</v>
@@ -3015,10 +3015,10 @@
         <v>2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.743404441826089</v>
+        <v>1.63100885458093</v>
       </c>
       <c r="U33" t="n">
-        <v>0.331246843946957</v>
+        <v>0.3098916823703767</v>
       </c>
       <c r="V33" t="n">
         <v>12.5</v>
@@ -3093,10 +3093,10 @@
         <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="U34" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="V34" t="n">
         <v>20</v>
@@ -3171,10 +3171,10 @@
         <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>0.6739106727341909</v>
+        <v>0.6224046427466493</v>
       </c>
       <c r="U35" t="n">
-        <v>0.1280430278194963</v>
+        <v>0.1182568821218634</v>
       </c>
       <c r="V35" t="n">
         <v>6</v>
@@ -3249,10 +3249,10 @@
         <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>1.123184454556985</v>
+        <v>1.037341071244415</v>
       </c>
       <c r="U36" t="n">
-        <v>0.2134050463658271</v>
+        <v>0.1970948035364389</v>
       </c>
       <c r="V36" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1.572458236379779</v>
+        <v>1.452277499742181</v>
       </c>
       <c r="U37" t="n">
-        <v>0.298767064912158</v>
+        <v>0.2759327249510145</v>
       </c>
       <c r="V37" t="n">
         <v>14</v>
@@ -3405,10 +3405,10 @@
         <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>0.9108902499594012</v>
+        <v>0.8558295263134812</v>
       </c>
       <c r="U38" t="n">
-        <v>0.1730691474922862</v>
+        <v>0.1626076099995614</v>
       </c>
       <c r="V38" t="n">
         <v>6</v>
@@ -3483,10 +3483,10 @@
         <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>1.366335374939102</v>
+        <v>1.283744289470222</v>
       </c>
       <c r="U39" t="n">
-        <v>0.2596037212384293</v>
+        <v>0.2439114149993421</v>
       </c>
       <c r="V39" t="n">
         <v>9</v>
@@ -3561,10 +3561,10 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>2.277225624898503</v>
+        <v>2.139573815783703</v>
       </c>
       <c r="U40" t="n">
-        <v>0.4326728687307156</v>
+        <v>0.4065190249989036</v>
       </c>
       <c r="V40" t="n">
         <v>15</v>
@@ -3639,10 +3639,10 @@
         <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>0.8072116849233715</v>
+        <v>0.7537061397529922</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1533702201354406</v>
+        <v>0.1432041665530685</v>
       </c>
       <c r="V41" t="n">
         <v>6</v>
@@ -3717,10 +3717,10 @@
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>1.345352808205619</v>
+        <v>1.25617689958832</v>
       </c>
       <c r="U42" t="n">
-        <v>0.2556170335590677</v>
+        <v>0.2386736109217809</v>
       </c>
       <c r="V42" t="n">
         <v>10</v>
@@ -3795,10 +3795,10 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>2.152564493128991</v>
+        <v>2.009883039341312</v>
       </c>
       <c r="U43" t="n">
-        <v>0.4089872536945083</v>
+        <v>0.3818777774748494</v>
       </c>
       <c r="V43" t="n">
         <v>16</v>
@@ -3873,10 +3873,10 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>1.046042665095654</v>
+        <v>0.9786053127485578</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1987481063681742</v>
+        <v>0.185935009422226</v>
       </c>
       <c r="V44" t="n">
         <v>7.5</v>
@@ -3951,10 +3951,10 @@
         <v>2</v>
       </c>
       <c r="T45" t="n">
-        <v>1.743404441826089</v>
+        <v>1.63100885458093</v>
       </c>
       <c r="U45" t="n">
-        <v>0.331246843946957</v>
+        <v>0.3098916823703767</v>
       </c>
       <c r="V45" t="n">
         <v>12.5</v>
@@ -4029,10 +4029,10 @@
         <v>3</v>
       </c>
       <c r="T46" t="n">
-        <v>2.789447106921743</v>
+        <v>2.609614167329487</v>
       </c>
       <c r="U46" t="n">
-        <v>0.5299949503151312</v>
+        <v>0.4958266917926026</v>
       </c>
       <c r="V46" t="n">
         <v>20</v>
@@ -4107,10 +4107,10 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.9331070853242645</v>
+        <v>0.8777131091478716</v>
       </c>
       <c r="U47" t="n">
-        <v>0.1772903462116102</v>
+        <v>0.1667654907380956</v>
       </c>
       <c r="V47" t="n">
         <v>6</v>
@@ -4185,10 +4185,10 @@
         <v>2</v>
       </c>
       <c r="T48" t="n">
-        <v>1.555178475540441</v>
+        <v>1.462855181913119</v>
       </c>
       <c r="U48" t="n">
-        <v>0.2954839103526837</v>
+        <v>0.2779424845634927</v>
       </c>
       <c r="V48" t="n">
         <v>10</v>
@@ -4263,10 +4263,10 @@
         <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>2.488285560864705</v>
+        <v>2.340568291060991</v>
       </c>
       <c r="U49" t="n">
-        <v>0.472774256564294</v>
+        <v>0.4447079753015883</v>
       </c>
       <c r="V49" t="n">
         <v>16</v>
@@ -4341,10 +4341,10 @@
         <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.9349584882713364</v>
+        <v>0.8691873985766052</v>
       </c>
       <c r="U50" t="n">
-        <v>0.1776421127715539</v>
+        <v>0.165145605729555</v>
       </c>
       <c r="V50" t="n">
         <v>7.5</v>
@@ -4401,7 +4401,7 @@
         <v>5</v>
       </c>
       <c r="N51" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="O51" t="n">
         <v>0.83</v>
@@ -4413,16 +4413,16 @@
         <v>0.35</v>
       </c>
       <c r="R51" t="n">
-        <v>0.735</v>
+        <v>0.738</v>
       </c>
       <c r="S51" t="n">
         <v>2</v>
       </c>
       <c r="T51" t="n">
-        <v>1.558264147118894</v>
+        <v>1.448645664294342</v>
       </c>
       <c r="U51" t="n">
-        <v>0.2960701879525898</v>
+        <v>0.275242676215925</v>
       </c>
       <c r="V51" t="n">
         <v>12.5</v>
@@ -4497,10 +4497,10 @@
         <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>2.49322263539023</v>
+        <v>2.317833062870947</v>
       </c>
       <c r="U52" t="n">
-        <v>0.4737123007241438</v>
+        <v>0.44038828194548</v>
       </c>
       <c r="V52" t="n">
         <v>20</v>
@@ -4557,7 +4557,7 @@
         <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="O53" t="n">
         <v>0.79</v>
@@ -4569,16 +4569,16 @@
         <v>0.15</v>
       </c>
       <c r="R53" t="n">
-        <v>0.633</v>
+        <v>0.63</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>2.229089148274632</v>
+        <v>2.099058947958611</v>
       </c>
       <c r="U53" t="n">
-        <v>0.4235269381721801</v>
+        <v>0.3988212001121362</v>
       </c>
       <c r="V53" t="n">
         <v>14</v>
@@ -4653,10 +4653,10 @@
         <v>2</v>
       </c>
       <c r="T54" t="n">
-        <v>3.343633722411948</v>
+        <v>3.148588421937917</v>
       </c>
       <c r="U54" t="n">
-        <v>0.6352904072582701</v>
+        <v>0.5982318001682043</v>
       </c>
       <c r="V54" t="n">
         <v>21</v>
@@ -4731,10 +4731,10 @@
         <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>4.458178296549264</v>
+        <v>4.198117895917223</v>
       </c>
       <c r="U55" t="n">
-        <v>0.8470538763443601</v>
+        <v>0.7976424002242724</v>
       </c>
       <c r="V55" t="n">
         <v>28</v>
@@ -4809,10 +4809,10 @@
         <v>3</v>
       </c>
       <c r="T56" t="n">
-        <v>0.6368826137927521</v>
+        <v>0.5859320046893317</v>
       </c>
       <c r="U56" t="n">
-        <v>0.1210076966206229</v>
+        <v>0.111327080890973</v>
       </c>
       <c r="V56" t="n">
         <v>6</v>
@@ -4887,10 +4887,10 @@
         <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>1.114544574137316</v>
+        <v>1.025381008206331</v>
       </c>
       <c r="U57" t="n">
-        <v>0.2117634690860901</v>
+        <v>0.1948223915592028</v>
       </c>
       <c r="V57" t="n">
         <v>10.5</v>
@@ -4965,10 +4965,10 @@
         <v>2</v>
       </c>
       <c r="T58" t="n">
-        <v>1.59220653448188</v>
+        <v>1.464830011723329</v>
       </c>
       <c r="U58" t="n">
-        <v>0.3025192415515572</v>
+        <v>0.2783177022274326</v>
       </c>
       <c r="V58" t="n">
         <v>15</v>
@@ -5025,7 +5025,7 @@
         <v>5</v>
       </c>
       <c r="N59" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="O59" t="n">
         <v>0.83</v>
@@ -5037,16 +5037,16 @@
         <v>0.15</v>
       </c>
       <c r="R59" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
       </c>
       <c r="T59" t="n">
-        <v>1.86683130496422</v>
+        <v>1.752584314771988</v>
       </c>
       <c r="U59" t="n">
-        <v>0.3546979479432018</v>
+        <v>0.3329910198066777</v>
       </c>
       <c r="V59" t="n">
         <v>12.5</v>
@@ -5121,10 +5121,10 @@
         <v>2</v>
       </c>
       <c r="T60" t="n">
-        <v>2.986930087942751</v>
+        <v>2.80413490363518</v>
       </c>
       <c r="U60" t="n">
-        <v>0.5675167167091227</v>
+        <v>0.5327856316906843</v>
       </c>
       <c r="V60" t="n">
         <v>20</v>
@@ -5199,10 +5199,10 @@
         <v>3</v>
       </c>
       <c r="T61" t="n">
-        <v>4.480395131914127</v>
+        <v>4.206202355452771</v>
       </c>
       <c r="U61" t="n">
-        <v>0.8512750750636842</v>
+        <v>0.7991784475360264</v>
       </c>
       <c r="V61" t="n">
         <v>30</v>
